--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD20C6C-3A12-4240-B792-A93B4A99014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84638E35-ACC2-49EC-9B8F-A7DFA8D43A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="86">
   <si>
     <t>BARKOD KODU</t>
   </si>
@@ -188,6 +188,96 @@
   </si>
   <si>
     <t>89397500-4</t>
+  </si>
+  <si>
+    <t>88580200-1</t>
+  </si>
+  <si>
+    <t>40002679</t>
+  </si>
+  <si>
+    <t>PRV 8.00MM-83HC</t>
+  </si>
+  <si>
+    <t>88580700-3</t>
+  </si>
+  <si>
+    <t>40002559</t>
+  </si>
+  <si>
+    <t>PRV 2.80MM-75MC</t>
+  </si>
+  <si>
+    <t>88452700-126</t>
+  </si>
+  <si>
+    <t>40002139</t>
+  </si>
+  <si>
+    <t>TF 5.50MM-75MC</t>
+  </si>
+  <si>
+    <t>89183200-20</t>
+  </si>
+  <si>
+    <t>000000000040002698</t>
+  </si>
+  <si>
+    <t>PRV 7.50MM-83HC</t>
+  </si>
+  <si>
+    <t>M515-WT</t>
+  </si>
+  <si>
+    <t>89183200-21</t>
+  </si>
+  <si>
+    <t>M140B</t>
+  </si>
+  <si>
+    <t>89183200-22</t>
+  </si>
+  <si>
+    <t>89183200-23</t>
+  </si>
+  <si>
+    <t>89183200-24</t>
+  </si>
+  <si>
+    <t>89183200-25</t>
+  </si>
+  <si>
+    <t>89183200-26</t>
+  </si>
+  <si>
+    <t>89183200-27</t>
+  </si>
+  <si>
+    <t>40002417</t>
+  </si>
+  <si>
+    <t>TV 2.20MM-83HC</t>
+  </si>
+  <si>
+    <t>40002156</t>
+  </si>
+  <si>
+    <t>TF 8.00MM-83HC</t>
+  </si>
+  <si>
+    <t>89366900-3</t>
+  </si>
+  <si>
+    <t>89369800-26</t>
+  </si>
+  <si>
+    <t>40002152</t>
+  </si>
+  <si>
+    <t>TF 5.50MM-83HC</t>
+  </si>
+  <si>
+    <t>89370100-1</t>
   </si>
 </sst>
 </file>
@@ -206,6 +296,8 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="3">
@@ -233,11 +325,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -258,8 +356,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M18">
-  <autoFilter ref="A1:M18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M32">
+  <autoFilter ref="A1:M32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BARKOD KODU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ÜRÜN KODU"/>
@@ -596,9 +694,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="2" customWidth="1"/>
   </cols>
@@ -1290,6 +1389,391 @@
         <v>46118.573773148099</v>
       </c>
     </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19">
+        <v>4954</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="5">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="5">
+        <v>12016</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22">
+        <v>9100</v>
+      </c>
+      <c r="E22">
+        <v>3155.88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46119.462893518503</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22">
+        <v>181608</v>
+      </c>
+      <c r="L22" t="s">
+        <v>47</v>
+      </c>
+      <c r="M22" s="2">
+        <v>46119.462893518503</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>9200</v>
+      </c>
+      <c r="E23">
+        <v>3190.56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46120.080833333297</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" t="s">
+        <v>47</v>
+      </c>
+      <c r="M23" s="2">
+        <v>46120.080833333297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24">
+        <v>9250</v>
+      </c>
+      <c r="E24">
+        <v>3207.9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46120.297164351898</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24">
+        <v>181608</v>
+      </c>
+      <c r="L24" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24" s="2">
+        <v>46120.297164351898</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25">
+        <v>9200</v>
+      </c>
+      <c r="E25">
+        <v>3190.56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46120.606817129599</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25">
+        <v>181608</v>
+      </c>
+      <c r="L25" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="2">
+        <v>46120.606817129599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26">
+        <v>9100</v>
+      </c>
+      <c r="E26">
+        <v>3155.88</v>
+      </c>
+      <c r="F26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2">
+        <v>46120.988449074102</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26">
+        <v>181608</v>
+      </c>
+      <c r="L26" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26" s="2">
+        <v>46120.988449074102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27">
+        <v>9200</v>
+      </c>
+      <c r="E27">
+        <v>3190.56</v>
+      </c>
+      <c r="F27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2">
+        <v>46121.415243055599</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27">
+        <v>181608</v>
+      </c>
+      <c r="L27" t="s">
+        <v>47</v>
+      </c>
+      <c r="M27" s="2">
+        <v>46121.415243055599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28">
+        <v>9300</v>
+      </c>
+      <c r="E28">
+        <v>3225.24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46121.621817129599</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28">
+        <v>181608</v>
+      </c>
+      <c r="L28" t="s">
+        <v>47</v>
+      </c>
+      <c r="M28" s="2">
+        <v>46121.621817129599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29">
+        <v>9200</v>
+      </c>
+      <c r="E29">
+        <v>3190.56</v>
+      </c>
+      <c r="F29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2">
+        <v>46122.121296296304</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29">
+        <v>181608</v>
+      </c>
+      <c r="L29" t="s">
+        <v>47</v>
+      </c>
+      <c r="M29" s="2">
+        <v>46122.121296296304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30">
+        <v>20067</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="5">
+        <v>6759</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -8,19 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84638E35-ACC2-49EC-9B8F-A7DFA8D43A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E48210-FA77-4FB5-920E-E3E2B2CC27F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VERİ" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
   <si>
     <t>BARKOD KODU</t>
   </si>
@@ -278,6 +295,81 @@
   </si>
   <si>
     <t>89370100-1</t>
+  </si>
+  <si>
+    <t>89456200-145</t>
+  </si>
+  <si>
+    <t>000000000040000813</t>
+  </si>
+  <si>
+    <t>HT 0.38MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>89466500-1</t>
+  </si>
+  <si>
+    <t>000000000040002501</t>
+  </si>
+  <si>
+    <t>PRV 1.92MM-70MC</t>
+  </si>
+  <si>
+    <t>89466500-3</t>
+  </si>
+  <si>
+    <t>89466500-4</t>
+  </si>
+  <si>
+    <t>89466500-5</t>
+  </si>
+  <si>
+    <t>89466500-6</t>
+  </si>
+  <si>
+    <t>89466500-7</t>
+  </si>
+  <si>
+    <t>89466500-8</t>
+  </si>
+  <si>
+    <t>89466500-9</t>
+  </si>
+  <si>
+    <t>89466500-2</t>
+  </si>
+  <si>
+    <t>89361200-7</t>
+  </si>
+  <si>
+    <t>000000000045028757</t>
+  </si>
+  <si>
+    <t>DMT 1X36WS-10.23MM-KT_B-200-S</t>
+  </si>
+  <si>
+    <t>M324-WT</t>
+  </si>
+  <si>
+    <t>89466500-10</t>
+  </si>
+  <si>
+    <t>89369200-2070</t>
+  </si>
+  <si>
+    <t>000000000040002165</t>
+  </si>
+  <si>
+    <t>TF 13.00MM-83PC</t>
+  </si>
+  <si>
+    <t>YT6</t>
+  </si>
+  <si>
+    <t>89537800-11</t>
+  </si>
+  <si>
+    <t>PRV 2.80MM-70MC</t>
   </si>
 </sst>
 </file>
@@ -325,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -336,6 +428,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,9 +448,49 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sayfa1"/>
+      <sheetName val="VERİ"/>
+      <sheetName val="16. Hafta P Filmaşin A360"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sayfa1"/>
+      <sheetName val="VERİ"/>
+      <sheetName val="16. Hafta P SAYIM"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M32">
-  <autoFilter ref="A1:M32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M46">
+  <autoFilter ref="A1:M46" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BARKOD KODU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ÜRÜN KODU"/>
@@ -694,12 +827,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1772,6 +1915,251 @@
       </c>
       <c r="D32" s="5">
         <v>6759</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33">
+        <v>11172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36">
+        <v>69000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39">
+        <v>70176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41">
+        <v>70176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42">
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43">
+        <v>559</v>
+      </c>
+      <c r="E43">
+        <v>314.15800000000002</v>
+      </c>
+      <c r="F43" t="s">
+        <v>103</v>
+      </c>
+      <c r="G43" s="2">
+        <v>46115.566956018498</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43">
+        <v>183446</v>
+      </c>
+      <c r="L43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M43" s="2">
+        <v>46115.566956018498</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44">
+        <v>40002501</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44">
+        <v>70176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45">
+        <v>1532</v>
+      </c>
+      <c r="E45">
+        <v>1596.3440000000001</v>
+      </c>
+      <c r="F45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G45" s="2">
+        <v>46125.3723032407</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" t="str">
+        <f>_xlfn.XLOOKUP([1]!Table1[[#This Row],[BARKOD KODU]],[2]!Table1[BOBİN BARKODU],[2]!Table1[SAYILAN MİKTAR (METRE)],"--")</f>
+        <v>--</v>
+      </c>
+      <c r="K45">
+        <v>893692</v>
+      </c>
+      <c r="M45" s="2">
+        <v>46125.3723032407</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46">
+        <v>40002515</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46">
+        <v>3100</v>
       </c>
     </row>
   </sheetData>

--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E48210-FA77-4FB5-920E-E3E2B2CC27F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F521A0-9DEF-48A0-86FF-002A0162561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="115">
   <si>
     <t>BARKOD KODU</t>
   </si>
@@ -370,6 +370,18 @@
   </si>
   <si>
     <t>PRV 2.80MM-70MC</t>
+  </si>
+  <si>
+    <t>89531100-2</t>
+  </si>
+  <si>
+    <t>000000000040002956</t>
+  </si>
+  <si>
+    <t>PRV 1.72MM-45MC</t>
+  </si>
+  <si>
+    <t>89531100-4</t>
   </si>
 </sst>
 </file>
@@ -489,8 +501,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M46">
-  <autoFilter ref="A1:M46" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M48">
+  <autoFilter ref="A1:M48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BARKOD KODU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ÜRÜN KODU"/>
@@ -827,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2162,6 +2174,76 @@
         <v>3100</v>
       </c>
     </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47">
+        <v>19050</v>
+      </c>
+      <c r="E47">
+        <v>346.71000000000004</v>
+      </c>
+      <c r="F47" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46132.072592592602</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" t="s">
+        <v>47</v>
+      </c>
+      <c r="M47" s="2">
+        <v>46132.072592592602</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48">
+        <v>10300</v>
+      </c>
+      <c r="E48">
+        <v>187.46</v>
+      </c>
+      <c r="F48" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46132.642789351798</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" t="s">
+        <v>47</v>
+      </c>
+      <c r="M48" s="2">
+        <v>46132.642789351798</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E73E79B-BB41-4D46-ADF9-8445539CC05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B49404B-CC33-40B0-A604-830D0D786C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>BARKOD KODU</t>
   </si>
@@ -72,6 +72,42 @@
   </si>
   <si>
     <t>ÜRETİM TARİHİ</t>
+  </si>
+  <si>
+    <t>89531000-2</t>
+  </si>
+  <si>
+    <t>000000000040002796</t>
+  </si>
+  <si>
+    <t>PRV 1.92MM-45MC</t>
+  </si>
+  <si>
+    <t>M140B</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>HAZIR</t>
+  </si>
+  <si>
+    <t>Euro Pallet</t>
+  </si>
+  <si>
+    <t>89531000-5</t>
+  </si>
+  <si>
+    <t>M511-WT</t>
+  </si>
+  <si>
+    <t>89547800-5</t>
+  </si>
+  <si>
+    <t>000000000040003659</t>
+  </si>
+  <si>
+    <t>PRV 1.55MM-45MC</t>
   </si>
 </sst>
 </file>
@@ -128,7 +164,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{12C1FC15-158E-40BB-BBDF-572893E54923}"/>
   </tableStyles>
@@ -144,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M2" insertRow="1">
-  <autoFilter ref="A1:M2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M4">
+  <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BARKOD KODU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ÜRÜN KODU"/>
@@ -153,13 +196,13 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="MİKTAR"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KG MİKTARI"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="LOKASYON"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="OLUŞTURMA ZAMANI"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="OLUŞTURMA ZAMANI" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="BİRİM KODU"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DURUM"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="BİRİM"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="SİPARİŞE BAĞLI"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ENVANTER TİPİ"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ÜRETİM TARİHİ"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ÜRETİM TARİHİ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -482,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -541,6 +584,111 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>54309.210526315801</v>
+      </c>
+      <c r="E2">
+        <v>1238.2500000000002</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>45000</v>
+      </c>
+      <c r="E3">
+        <v>1026</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>110000</v>
+      </c>
+      <c r="E4">
+        <v>1628</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B49404B-CC33-40B0-A604-830D0D786C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8437CEF-7E04-44D1-8345-AEBA8F3A98F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="161">
   <si>
     <t>BARKOD KODU</t>
   </si>
@@ -108,6 +108,414 @@
   </si>
   <si>
     <t>PRV 1.55MM-45MC</t>
+  </si>
+  <si>
+    <t>89265400-18</t>
+  </si>
+  <si>
+    <t>000000000040002596</t>
+  </si>
+  <si>
+    <t>PRV 2.20MM-83HC</t>
+  </si>
+  <si>
+    <t>89387200-43</t>
+  </si>
+  <si>
+    <t>000000000040002674</t>
+  </si>
+  <si>
+    <t>PRV 2.50MM-70MC</t>
+  </si>
+  <si>
+    <t>89387200-54</t>
+  </si>
+  <si>
+    <t>89422700-10</t>
+  </si>
+  <si>
+    <t>000000000040002630</t>
+  </si>
+  <si>
+    <t>PRV 5.00MM-83HC</t>
+  </si>
+  <si>
+    <t>89446900-5</t>
+  </si>
+  <si>
+    <t>000000000040002502</t>
+  </si>
+  <si>
+    <t>PRV 2.00MM-70MC</t>
+  </si>
+  <si>
+    <t>89466300-11</t>
+  </si>
+  <si>
+    <t>000000000040002573</t>
+  </si>
+  <si>
+    <t>PRV 4.00MM-75MC</t>
+  </si>
+  <si>
+    <t>89507300-1</t>
+  </si>
+  <si>
+    <t>000000000040002628</t>
+  </si>
+  <si>
+    <t>PRV 4.80MM-83HC</t>
+  </si>
+  <si>
+    <t>89530400-2</t>
+  </si>
+  <si>
+    <t>000000000040002621</t>
+  </si>
+  <si>
+    <t>PRV 4.25MM-83HC</t>
+  </si>
+  <si>
+    <t>89537800-3</t>
+  </si>
+  <si>
+    <t>000000000040002515</t>
+  </si>
+  <si>
+    <t>PRV 2.80MM-70MC</t>
+  </si>
+  <si>
+    <t>89570800-2</t>
+  </si>
+  <si>
+    <t>000000000040002527</t>
+  </si>
+  <si>
+    <t>PRV 4.00MM-70MC</t>
+  </si>
+  <si>
+    <t>89574600-7</t>
+  </si>
+  <si>
+    <t>000000000040002550</t>
+  </si>
+  <si>
+    <t>PRV 2.00MM-75MC</t>
+  </si>
+  <si>
+    <t>89585300-1</t>
+  </si>
+  <si>
+    <t>000000000040002565</t>
+  </si>
+  <si>
+    <t>PRV 3.20MM-75MC</t>
+  </si>
+  <si>
+    <t>89606400-2</t>
+  </si>
+  <si>
+    <t>000000000040002159</t>
+  </si>
+  <si>
+    <t>TF 11.00MM-83HC</t>
+  </si>
+  <si>
+    <t>M180</t>
+  </si>
+  <si>
+    <t>72915700-247</t>
+  </si>
+  <si>
+    <t>000000000040002732</t>
+  </si>
+  <si>
+    <t>TG 2.30MM-KT_B-83HC</t>
+  </si>
+  <si>
+    <t>M140B-WT</t>
+  </si>
+  <si>
+    <t>M140 Buyuk Boy Sepet</t>
+  </si>
+  <si>
+    <t>88063600-8</t>
+  </si>
+  <si>
+    <t>000000000040002906</t>
+  </si>
+  <si>
+    <t>TG 1.55MM-KT_C-83HC</t>
+  </si>
+  <si>
+    <t>M132</t>
+  </si>
+  <si>
+    <t>89447000-8</t>
+  </si>
+  <si>
+    <t>000000000040002413</t>
+  </si>
+  <si>
+    <t>TV 1.70MM-83HC</t>
+  </si>
+  <si>
+    <t>M131</t>
+  </si>
+  <si>
+    <t>80784000-146</t>
+  </si>
+  <si>
+    <t>000000000040003212</t>
+  </si>
+  <si>
+    <t>TG 3.30MM-KT_B-75MC</t>
+  </si>
+  <si>
+    <t>M186</t>
+  </si>
+  <si>
+    <t>80784000-154</t>
+  </si>
+  <si>
+    <t>M185</t>
+  </si>
+  <si>
+    <t>89387800-27</t>
+  </si>
+  <si>
+    <t>000000000040002372</t>
+  </si>
+  <si>
+    <t>TV 2.00MM-70MC</t>
+  </si>
+  <si>
+    <t>M194</t>
+  </si>
+  <si>
+    <t>89388300-9</t>
+  </si>
+  <si>
+    <t>000000000040002854</t>
+  </si>
+  <si>
+    <t>TG 4.10MM-KT_B-75MC</t>
+  </si>
+  <si>
+    <t>M184</t>
+  </si>
+  <si>
+    <t>89408900-22</t>
+  </si>
+  <si>
+    <t>000000000040002370</t>
+  </si>
+  <si>
+    <t>TV 1.80MM-70MC</t>
+  </si>
+  <si>
+    <t>M127</t>
+  </si>
+  <si>
+    <t>89408900-23</t>
+  </si>
+  <si>
+    <t>89447000-28</t>
+  </si>
+  <si>
+    <t>89468100-3</t>
+  </si>
+  <si>
+    <t>000000000040002801</t>
+  </si>
+  <si>
+    <t>TG 1.85MM-KT_B-75MC</t>
+  </si>
+  <si>
+    <t>M125</t>
+  </si>
+  <si>
+    <t>89547600-4</t>
+  </si>
+  <si>
+    <t>000000000040003449</t>
+  </si>
+  <si>
+    <t>TG 4.60MM-KT_C-75MC</t>
+  </si>
+  <si>
+    <t>89547600-7</t>
+  </si>
+  <si>
+    <t>M116</t>
+  </si>
+  <si>
+    <t>89564900-4</t>
+  </si>
+  <si>
+    <t>000000000040002926</t>
+  </si>
+  <si>
+    <t>TG 4.30MM-KT_B-70MC</t>
+  </si>
+  <si>
+    <t>89469300-3</t>
+  </si>
+  <si>
+    <t>89469900-6</t>
+  </si>
+  <si>
+    <t>000000000040002281</t>
+  </si>
+  <si>
+    <t>TG 4.60MM-KT_B-83HC</t>
+  </si>
+  <si>
+    <t>M177</t>
+  </si>
+  <si>
+    <t>89549600-28</t>
+  </si>
+  <si>
+    <t>000000000040002434</t>
+  </si>
+  <si>
+    <t>TV 4.80MM-83HC</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>89132500-15</t>
+  </si>
+  <si>
+    <t>89183500-5</t>
+  </si>
+  <si>
+    <t>000000000040002594</t>
+  </si>
+  <si>
+    <t>PRV 2.00MM-83HC</t>
+  </si>
+  <si>
+    <t>89310000-7</t>
+  </si>
+  <si>
+    <t>000000000040002601</t>
+  </si>
+  <si>
+    <t>PRV 2.50MM-83HC</t>
+  </si>
+  <si>
+    <t>89387000-20</t>
+  </si>
+  <si>
+    <t>000000000040002510</t>
+  </si>
+  <si>
+    <t>PRV 2.40MM-70MC</t>
+  </si>
+  <si>
+    <t>89387000-21</t>
+  </si>
+  <si>
+    <t>89466300-7</t>
+  </si>
+  <si>
+    <t>89485900-14</t>
+  </si>
+  <si>
+    <t>000000000040002505</t>
+  </si>
+  <si>
+    <t>PRV 2.20MM-70MC</t>
+  </si>
+  <si>
+    <t>89485900-15</t>
+  </si>
+  <si>
+    <t>89530400-3</t>
+  </si>
+  <si>
+    <t>89585200-1</t>
+  </si>
+  <si>
+    <t>000000000040002580</t>
+  </si>
+  <si>
+    <t>PRV 5.00MM-75MC</t>
+  </si>
+  <si>
+    <t>89585200-2</t>
+  </si>
+  <si>
+    <t>89585300-4</t>
+  </si>
+  <si>
+    <t>89479400-2</t>
+  </si>
+  <si>
+    <t>PRV 2.80MM-83HC</t>
+  </si>
+  <si>
+    <t>89485800-6</t>
+  </si>
+  <si>
+    <t>PRV 4.50MM-75MC</t>
+  </si>
+  <si>
+    <t>89530600-4</t>
+  </si>
+  <si>
+    <t>PRV 2.50MM-75MC</t>
+  </si>
+  <si>
+    <t>89549900-7</t>
+  </si>
+  <si>
+    <t>PRV 2.20MM-75MC</t>
+  </si>
+  <si>
+    <t>89549900-9</t>
+  </si>
+  <si>
+    <t>89585300-6</t>
+  </si>
+  <si>
+    <t>89585600-1</t>
+  </si>
+  <si>
+    <t>PRV 1.95MM-55MC</t>
+  </si>
+  <si>
+    <t>89641200-2</t>
+  </si>
+  <si>
+    <t>PRV 3.20MM-70MC</t>
+  </si>
+  <si>
+    <t>89642100-8</t>
+  </si>
+  <si>
+    <t>PRV 3.50MM-75MC</t>
+  </si>
+  <si>
+    <t>89662400-2</t>
+  </si>
+  <si>
+    <t>PRV 3.80MM-83HC</t>
+  </si>
+  <si>
+    <t>M140-S23</t>
+  </si>
+  <si>
+    <t>SARICI</t>
+  </si>
+  <si>
+    <t>M140-S30</t>
+  </si>
+  <si>
+    <t>PRV 6.40MM-83HC (TGB)</t>
   </si>
 </sst>
 </file>
@@ -155,21 +563,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -187,14 +602,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M4">
-  <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M58">
+  <autoFilter ref="A1:M58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BARKOD KODU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ÜRÜN KODU"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ÜRÜN"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="MİKTAR"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KG MİKTARI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="MİKTAR" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KG MİKTARI" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="LOKASYON"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="OLUŞTURMA ZAMANI" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="BİRİM KODU"/>
@@ -525,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -594,10 +1009,10 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>54309.210526315801</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>1238.2500000000002</v>
       </c>
       <c r="F2" t="s">
@@ -629,10 +1044,10 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>45000</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>1026</v>
       </c>
       <c r="F3" t="s">
@@ -664,10 +1079,10 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>110000</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>1628</v>
       </c>
       <c r="F4" t="s">
@@ -687,6 +1102,1923 @@
       </c>
       <c r="M4" s="2">
         <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4">
+        <v>910</v>
+      </c>
+      <c r="E5" s="4">
+        <v>27.209</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46148.346759259301</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="2">
+        <v>46148.346759259301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1438</v>
+      </c>
+      <c r="E6" s="4">
+        <v>55.363</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2460</v>
+      </c>
+      <c r="E7" s="4">
+        <v>94.71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4">
+        <v>811</v>
+      </c>
+      <c r="E8" s="4">
+        <v>125.0562</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="4">
+        <v>22384.14</v>
+      </c>
+      <c r="E9" s="4">
+        <v>552.88825799999995</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46146.488761574103</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="2">
+        <v>46146.488761574103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2110.0050658561013</v>
+      </c>
+      <c r="E10" s="4">
+        <v>208.25749999999718</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="4">
+        <v>7862.0056298381005</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1117.1909999999941</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="4">
+        <v>13513.147217235201</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1505.3646000000012</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46146.567071759302</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="2">
+        <v>46146.567071759302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="4">
+        <v>15571.900826446279</v>
+      </c>
+      <c r="E13" s="4">
+        <v>753.67999999999984</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="4">
+        <v>755.98074974670999</v>
+      </c>
+      <c r="E14" s="4">
+        <v>74.615300000000275</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="4">
+        <v>47172.077651821892</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1165.1503180000007</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="2">
+        <v>46146.488761574103</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="2">
+        <v>46146.488761574103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="4">
+        <v>8705</v>
+      </c>
+      <c r="E16" s="4">
+        <v>550.15600000000006</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1141.82</v>
+      </c>
+      <c r="E17" s="4">
+        <v>851.91190199999994</v>
+      </c>
+      <c r="F17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46146.725462962997</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17">
+        <v>184659</v>
+      </c>
+      <c r="M17" s="2">
+        <v>46146.725462962997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="4">
+        <v>7300.6134969325203</v>
+      </c>
+      <c r="E18" s="4">
+        <v>238.00000000000014</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4054.0540540540501</v>
+      </c>
+      <c r="E19" s="4">
+        <v>59.999999999999943</v>
+      </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="4">
+        <v>6256.9832402234597</v>
+      </c>
+      <c r="E20" s="4">
+        <v>111.99999999999993</v>
+      </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1444.5733333332901</v>
+      </c>
+      <c r="E21" s="4">
+        <v>97.075327999997086</v>
+      </c>
+      <c r="F21" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21">
+        <v>184650</v>
+      </c>
+      <c r="L21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1368.4290476189999</v>
+      </c>
+      <c r="E22" s="4">
+        <v>91.95843199999679</v>
+      </c>
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22">
+        <v>185788</v>
+      </c>
+      <c r="L22" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="4">
+        <v>906.3587854251</v>
+      </c>
+      <c r="E23" s="4">
+        <v>22.387061999999968</v>
+      </c>
+      <c r="F23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23">
+        <v>185490</v>
+      </c>
+      <c r="L23" t="s">
+        <v>67</v>
+      </c>
+      <c r="M23" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="4">
+        <v>554.93999999999903</v>
+      </c>
+      <c r="E24" s="4">
+        <v>57.491783999999896</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46148.984363425901</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24">
+        <v>186348</v>
+      </c>
+      <c r="L24" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24" s="2">
+        <v>46148.984363425901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3016.5599999999899</v>
+      </c>
+      <c r="E25" s="4">
+        <v>60.331199999999797</v>
+      </c>
+      <c r="F25" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25">
+        <v>185507</v>
+      </c>
+      <c r="L25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3692.26</v>
+      </c>
+      <c r="E26" s="4">
+        <v>73.845200000000006</v>
+      </c>
+      <c r="F26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26">
+        <v>185976</v>
+      </c>
+      <c r="L26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2794</v>
+      </c>
+      <c r="E27" s="4">
+        <v>50.012599999999999</v>
+      </c>
+      <c r="F27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="2">
+        <v>46147.636608796303</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27">
+        <v>184370</v>
+      </c>
+      <c r="L27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M27" s="2">
+        <v>46147.636608796303</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3222.7488151658799</v>
+      </c>
+      <c r="E28" s="4">
+        <v>68.000000000000071</v>
+      </c>
+      <c r="F28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" t="s">
+        <v>67</v>
+      </c>
+      <c r="M28" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="4">
+        <v>524.48490421456052</v>
+      </c>
+      <c r="E29" s="4">
+        <v>68.445280000000153</v>
+      </c>
+      <c r="F29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M29" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="4">
+        <v>595.44827586206998</v>
+      </c>
+      <c r="E30" s="4">
+        <v>77.706000000000131</v>
+      </c>
+      <c r="F30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30">
+        <v>185545</v>
+      </c>
+      <c r="L30" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="4">
+        <v>477.09000000000015</v>
+      </c>
+      <c r="E31" s="4">
+        <v>54.388260000000017</v>
+      </c>
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>67</v>
+      </c>
+      <c r="M31" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5600</v>
+      </c>
+      <c r="E32" s="4">
+        <v>112</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" t="s">
+        <v>67</v>
+      </c>
+      <c r="M32" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1486.59003831418</v>
+      </c>
+      <c r="E33" s="4">
+        <v>194.00000000000048</v>
+      </c>
+      <c r="F33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="2">
+        <v>46146.488726851901</v>
+      </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" t="s">
+        <v>67</v>
+      </c>
+      <c r="M33" s="2">
+        <v>46146.488726851901</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1535.23</v>
+      </c>
+      <c r="E34" s="4">
+        <v>218.156183</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="2">
+        <v>46147.4124421296</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34">
+        <v>185034</v>
+      </c>
+      <c r="L34" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34" s="2">
+        <v>46147.4124421296</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1530.6801619432954</v>
+      </c>
+      <c r="E35" s="4">
+        <v>37.807799999999396</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="4">
+        <v>7771.8906882590964</v>
+      </c>
+      <c r="E36" s="4">
+        <v>191.96569999999969</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="4">
+        <v>11342.103626943001</v>
+      </c>
+      <c r="E37" s="4">
+        <v>437.80519999999984</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="4">
+        <v>9470</v>
+      </c>
+      <c r="E38" s="4">
+        <v>337.13200000000001</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="4">
+        <v>7022.4719101123601</v>
+      </c>
+      <c r="E39" s="4">
+        <v>250.00000000000003</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2451.3080040526984</v>
+      </c>
+      <c r="E40" s="4">
+        <v>241.94410000000133</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="4">
+        <v>10993</v>
+      </c>
+      <c r="E41" s="4">
+        <v>328.69069999999999</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="2">
+        <v>46146.969189814801</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="2">
+        <v>46146.969189814801</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="4">
+        <v>9812</v>
+      </c>
+      <c r="E42" s="4">
+        <v>293.37880000000001</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="2">
+        <v>46147.061747685198</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" s="2">
+        <v>46147.061747685198</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="4">
+        <v>17566.965888689399</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1956.9599999999991</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1063</v>
+      </c>
+      <c r="E44" s="4">
+        <v>163.91460000000001</v>
+      </c>
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" s="4">
+        <v>369</v>
+      </c>
+      <c r="E45" s="4">
+        <v>56.899799999999999</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="4">
+        <v>3341</v>
+      </c>
+      <c r="E46" s="4">
+        <v>211.15120000000002</v>
+      </c>
+      <c r="F46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" t="s">
+        <v>19</v>
+      </c>
+      <c r="M46" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47">
+        <v>40002605</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="4">
+        <v>5990</v>
+      </c>
+      <c r="E47" s="4">
+        <v>289.916</v>
+      </c>
+      <c r="F47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46146.488738425898</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" t="s">
+        <v>19</v>
+      </c>
+      <c r="M47" s="2">
+        <v>46146.488738425898</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48">
+        <v>40002575</v>
+      </c>
+      <c r="C48" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2395</v>
+      </c>
+      <c r="E48" s="4">
+        <v>299.13549999999998</v>
+      </c>
+      <c r="F48" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46147.496226851901</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" t="s">
+        <v>19</v>
+      </c>
+      <c r="M48" s="2">
+        <v>46147.496226851901</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49">
+        <v>40002555</v>
+      </c>
+      <c r="C49" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="4">
+        <v>12289.3575129534</v>
+      </c>
+      <c r="E49" s="4">
+        <v>474.36920000000129</v>
+      </c>
+      <c r="F49" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="2">
+        <v>46146.488749999997</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="2">
+        <v>46146.488749999997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50">
+        <v>40002552</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="4">
+        <v>40</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1.196</v>
+      </c>
+      <c r="F50" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="2">
+        <v>46147.246168981503</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" s="2">
+        <v>46147.246168981503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51">
+        <v>40002552</v>
+      </c>
+      <c r="C51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="4">
+        <v>2335</v>
+      </c>
+      <c r="E51" s="4">
+        <v>69.816500000000005</v>
+      </c>
+      <c r="F51" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="2">
+        <v>46147.467789351896</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="2">
+        <v>46147.467789351896</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52">
+        <v>40002565</v>
+      </c>
+      <c r="C52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="4">
+        <v>717</v>
+      </c>
+      <c r="E52" s="4">
+        <v>45.314400000000006</v>
+      </c>
+      <c r="F52" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="2">
+        <v>46146.648101851897</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>19</v>
+      </c>
+      <c r="M52" s="2">
+        <v>46146.648101851897</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53">
+        <v>40003692</v>
+      </c>
+      <c r="C53" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="4">
+        <v>11415</v>
+      </c>
+      <c r="E53" s="4">
+        <v>267.11099999999999</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="2">
+        <v>46147.376226851899</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" t="s">
+        <v>19</v>
+      </c>
+      <c r="M53" s="2">
+        <v>46147.376226851899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54">
+        <v>40002520</v>
+      </c>
+      <c r="C54" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="4">
+        <v>3439</v>
+      </c>
+      <c r="E54" s="4">
+        <v>217.34480000000002</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="2">
+        <v>46148.232812499999</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="2">
+        <v>46148.232812499999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55">
+        <v>40002567</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="4">
+        <v>2360</v>
+      </c>
+      <c r="E55" s="4">
+        <v>178.416</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="2">
+        <v>46151.232233796298</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="2">
+        <v>46151.232233796298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>155</v>
+      </c>
+      <c r="B56">
+        <v>40002616</v>
+      </c>
+      <c r="C56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" s="4">
+        <v>490</v>
+      </c>
+      <c r="E56" s="4">
+        <v>43.658999999999999</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="2">
+        <v>46150.389652777798</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" t="s">
+        <v>19</v>
+      </c>
+      <c r="M56" s="2">
+        <v>46150.389652777798</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57">
+        <v>40002505</v>
+      </c>
+      <c r="C57" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="4">
+        <v>4107</v>
+      </c>
+      <c r="E57" s="4">
+        <v>122.7993</v>
+      </c>
+      <c r="F57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="2">
+        <v>46148.516423611101</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" t="s">
+        <v>158</v>
+      </c>
+      <c r="M57" s="2">
+        <v>46148.516423611101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58">
+        <v>40003475</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="4">
+        <v>2799.0198019802001</v>
+      </c>
+      <c r="E58" s="4">
+        <v>706.75250000000051</v>
+      </c>
+      <c r="F58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="2">
+        <v>46146.565185185202</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" t="s">
+        <v>158</v>
+      </c>
+      <c r="M58" s="2">
+        <v>46146.565185185202</v>
       </c>
     </row>
   </sheetData>

--- a/Stok Kontrol/Silinen.xlsx
+++ b/Stok Kontrol/Silinen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD4F2A0-E194-4A4F-9AF4-52C55D260587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A721B1FD-DB94-465C-92D2-5A435A694C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,31 +68,31 @@
     <t>SİPARİŞE BAĞLI</t>
   </si>
   <si>
-    <t>ENVANTER TİPİ</t>
-  </si>
-  <si>
-    <t>ÜRETİM TARİHİ</t>
-  </si>
-  <si>
-    <t>89531000-2</t>
-  </si>
-  <si>
-    <t>000000000040002796</t>
-  </si>
-  <si>
-    <t>PRV 1.92MM-45MC</t>
+    <t>M</t>
+  </si>
+  <si>
+    <t>HAZIR</t>
+  </si>
+  <si>
+    <t>Euro Pallet</t>
   </si>
   <si>
     <t>M140B</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>HAZIR</t>
-  </si>
-  <si>
-    <t>Euro Pallet</t>
+    <t>000000000040002527</t>
+  </si>
+  <si>
+    <t>PRV 4.00MM-70MC</t>
+  </si>
+  <si>
+    <t>90015600-2</t>
+  </si>
+  <si>
+    <t>AÇIKLAMA</t>
+  </si>
+  <si>
+    <t>TARİH</t>
   </si>
 </sst>
 </file>
@@ -193,8 +193,8 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DURUM"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="BİRİM"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="SİPARİŞE BAĞLI"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ENVANTER TİPİ"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ÜRETİM TARİHİ" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="AÇIKLAMA"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="TARİH" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -570,45 +570,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>111.4323</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46199.461562500001</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>54309.210526315801</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1238.2500000000002</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46146.488749999997</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2">
-        <v>46146.488749999997</v>
       </c>
     </row>
   </sheetData>
